--- a/workbook/AKI_selective_outcome_v32_all_tables_reproducible.xlsx
+++ b/workbook/AKI_selective_outcome_v32_all_tables_reproducible.xlsx
@@ -534,7 +534,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Missing postoperative creatinine outcomes study v3.2.3</t>
+          <t>Selective outcome observation study v3.2.4</t>
         </is>
       </c>
     </row>

--- a/workbook/AKI_selective_outcome_v32_all_tables_reproducible.xlsx
+++ b/workbook/AKI_selective_outcome_v32_all_tables_reproducible.xlsx
@@ -534,7 +534,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Selective outcome observation study v3.2.4</t>
+          <t>Selective outcome observation study v3.2.5</t>
         </is>
       </c>
     </row>
